--- a/FORMULÁRIO QUALITATIVO 2026 (respostas).xlsx
+++ b/FORMULÁRIO QUALITATIVO 2026 (respostas).xlsx
@@ -6,14 +6,14 @@
     <sheet state="visible" name="Respostas ao formulário 1" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'Respostas ao formulário 1'!$A$1:$AA$72</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'Respostas ao formulário 1'!$A$1:$AA$100</definedName>
   </definedNames>
   <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="94">
   <si>
     <t>Carimbo de data/hora</t>
   </si>
@@ -271,6 +271,30 @@
   </si>
   <si>
     <t>PÁTIO/ESTACIONAMENTO, MANUTENÇÃO PREVENTIVA, ESPAÇO INFANTIL</t>
+  </si>
+  <si>
+    <t>Maringá velho</t>
+  </si>
+  <si>
+    <t>PÁTIO/ESTACIONAMENTO</t>
+  </si>
+  <si>
+    <t>MANUTENÇÃO PREVENTIVA</t>
+  </si>
+  <si>
+    <t>BR 14-2362 - MARINGÁ VELHO</t>
+  </si>
+  <si>
+    <t>00</t>
+  </si>
+  <si>
+    <t>BR 14-1399 - JARDIM VERÔNICA</t>
+  </si>
+  <si>
+    <t>LIMPEZA, GEM, MANUTENÇÃO PREVENTIVA, ESPAÇO INFANTIL</t>
+  </si>
+  <si>
+    <t>09</t>
   </si>
 </sst>
 </file>
@@ -423,8 +447,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:AA72" displayName="Form_Responses" name="Form_Responses" id="1">
-  <autoFilter ref="$A$1:$AA$72"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:AA100" displayName="Form_Responses" name="Form_Responses" id="1">
+  <autoFilter ref="$A$1:$AA$100">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="08"/>
+        <filter val="8"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="27">
     <tableColumn name="Carimbo de data/hora" id="1"/>
     <tableColumn name="MÊS" id="2"/>
@@ -762,7 +793,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" ht="22.5" customHeight="1">
+    <row r="2" ht="22.5" hidden="1" customHeight="1">
       <c r="A2" s="3">
         <v>46161.66699090278</v>
       </c>
@@ -839,7 +870,7 @@
       </c>
       <c r="AA2" s="7"/>
     </row>
-    <row r="3" ht="22.5" customHeight="1">
+    <row r="3" ht="22.5" hidden="1" customHeight="1">
       <c r="A3" s="3">
         <v>46161.717658842594</v>
       </c>
@@ -916,7 +947,7 @@
       </c>
       <c r="AA3" s="7"/>
     </row>
-    <row r="4" ht="22.5" customHeight="1">
+    <row r="4" ht="22.5" hidden="1" customHeight="1">
       <c r="A4" s="3">
         <v>46162.32503172454</v>
       </c>
@@ -981,7 +1012,7 @@
       </c>
       <c r="AA4" s="7"/>
     </row>
-    <row r="5" ht="22.5" customHeight="1">
+    <row r="5" ht="22.5" hidden="1" customHeight="1">
       <c r="A5" s="3">
         <v>46162.49362635417</v>
       </c>
@@ -1026,7 +1057,7 @@
       </c>
       <c r="AA5" s="7"/>
     </row>
-    <row r="6" ht="22.5" customHeight="1">
+    <row r="6" ht="22.5" hidden="1" customHeight="1">
       <c r="A6" s="3">
         <v>46162.55207898148</v>
       </c>
@@ -1071,7 +1102,7 @@
       </c>
       <c r="AA6" s="7"/>
     </row>
-    <row r="7" ht="22.5" customHeight="1">
+    <row r="7" ht="22.5" hidden="1" customHeight="1">
       <c r="A7" s="3">
         <v>46165.76160042824</v>
       </c>
@@ -1128,7 +1159,7 @@
       </c>
       <c r="AA7" s="7"/>
     </row>
-    <row r="8" ht="22.5" customHeight="1">
+    <row r="8" ht="22.5" hidden="1" customHeight="1">
       <c r="A8" s="8">
         <v>46168.36660253472</v>
       </c>
@@ -1176,7 +1207,7 @@
       </c>
       <c r="AA8" s="11"/>
     </row>
-    <row r="9" ht="22.5" customHeight="1">
+    <row r="9" ht="22.5" hidden="1" customHeight="1">
       <c r="A9" s="8">
         <v>46169.744550648145</v>
       </c>
@@ -1251,7 +1282,7 @@
       </c>
       <c r="AA9" s="11"/>
     </row>
-    <row r="10" ht="22.5" customHeight="1">
+    <row r="10" ht="22.5" hidden="1" customHeight="1">
       <c r="A10" s="8">
         <v>46169.90514916666</v>
       </c>
@@ -1326,7 +1357,7 @@
       </c>
       <c r="AA10" s="11"/>
     </row>
-    <row r="11" ht="22.5" customHeight="1">
+    <row r="11" ht="22.5" hidden="1" customHeight="1">
       <c r="A11" s="8">
         <v>46172.67972921296</v>
       </c>
@@ -1347,7 +1378,7 @@
       </c>
       <c r="AA11" s="11"/>
     </row>
-    <row r="12" ht="22.5" customHeight="1">
+    <row r="12" ht="22.5" hidden="1" customHeight="1">
       <c r="A12" s="8">
         <v>46172.697124618055</v>
       </c>
@@ -1404,7 +1435,7 @@
       </c>
       <c r="AA12" s="11"/>
     </row>
-    <row r="13" ht="22.5" customHeight="1">
+    <row r="13" ht="22.5" hidden="1" customHeight="1">
       <c r="A13" s="8">
         <v>46172.7069606713</v>
       </c>
@@ -1431,7 +1462,7 @@
       </c>
       <c r="AA13" s="11"/>
     </row>
-    <row r="14" ht="22.5" customHeight="1">
+    <row r="14" ht="22.5" hidden="1" customHeight="1">
       <c r="A14" s="8">
         <v>46172.70767744213</v>
       </c>
@@ -1455,7 +1486,7 @@
       </c>
       <c r="AA14" s="11"/>
     </row>
-    <row r="15" ht="22.5" customHeight="1">
+    <row r="15" ht="22.5" hidden="1" customHeight="1">
       <c r="A15" s="8">
         <v>46172.7086074074</v>
       </c>
@@ -1488,7 +1519,7 @@
       </c>
       <c r="AA15" s="11"/>
     </row>
-    <row r="16" ht="22.5" customHeight="1">
+    <row r="16" ht="22.5" hidden="1" customHeight="1">
       <c r="A16" s="8">
         <v>46173.51154100694</v>
       </c>
@@ -1518,7 +1549,7 @@
       </c>
       <c r="AA16" s="11"/>
     </row>
-    <row r="17" ht="22.5" customHeight="1">
+    <row r="17" ht="22.5" hidden="1" customHeight="1">
       <c r="A17" s="8">
         <v>46173.86278575231</v>
       </c>
@@ -1545,7 +1576,7 @@
       </c>
       <c r="AA17" s="11"/>
     </row>
-    <row r="18" ht="22.5" customHeight="1">
+    <row r="18" ht="22.5" hidden="1" customHeight="1">
       <c r="A18" s="8">
         <v>46174.63476946759</v>
       </c>
@@ -1575,7 +1606,7 @@
       </c>
       <c r="AA18" s="11"/>
     </row>
-    <row r="19" ht="22.5" customHeight="1">
+    <row r="19" ht="22.5" hidden="1" customHeight="1">
       <c r="A19" s="8">
         <v>46174.66969215278</v>
       </c>
@@ -1641,7 +1672,7 @@
       </c>
       <c r="AA19" s="11"/>
     </row>
-    <row r="20" ht="22.5" customHeight="1">
+    <row r="20" ht="22.5" hidden="1" customHeight="1">
       <c r="A20" s="8">
         <v>46174.74549342593</v>
       </c>
@@ -1698,7 +1729,7 @@
       </c>
       <c r="AA20" s="11"/>
     </row>
-    <row r="21" ht="22.5" customHeight="1">
+    <row r="21" ht="22.5" hidden="1" customHeight="1">
       <c r="A21" s="8">
         <v>46176.80739381944</v>
       </c>
@@ -1740,7 +1771,7 @@
       </c>
       <c r="AA21" s="11"/>
     </row>
-    <row r="22" ht="22.5" customHeight="1">
+    <row r="22" ht="22.5" hidden="1" customHeight="1">
       <c r="A22" s="8">
         <v>46178.44168116898</v>
       </c>
@@ -1779,7 +1810,7 @@
       </c>
       <c r="AA22" s="11"/>
     </row>
-    <row r="23" ht="22.5" customHeight="1">
+    <row r="23" ht="22.5" hidden="1" customHeight="1">
       <c r="A23" s="8">
         <v>46179.84200296296</v>
       </c>
@@ -1809,7 +1840,7 @@
       </c>
       <c r="AA23" s="11"/>
     </row>
-    <row r="24" ht="22.5" customHeight="1">
+    <row r="24" ht="22.5" hidden="1" customHeight="1">
       <c r="A24" s="8">
         <v>46181.528076828705</v>
       </c>
@@ -1830,7 +1861,7 @@
       </c>
       <c r="AA24" s="11"/>
     </row>
-    <row r="25" ht="22.5" customHeight="1">
+    <row r="25" ht="22.5" hidden="1" customHeight="1">
       <c r="A25" s="8">
         <v>46181.86944918981</v>
       </c>
@@ -1860,7 +1891,7 @@
       </c>
       <c r="AA25" s="11"/>
     </row>
-    <row r="26" ht="22.5" customHeight="1">
+    <row r="26" ht="22.5" hidden="1" customHeight="1">
       <c r="A26" s="8">
         <v>46181.870301689814</v>
       </c>
@@ -1890,7 +1921,7 @@
       </c>
       <c r="AA26" s="11"/>
     </row>
-    <row r="27" ht="22.5" customHeight="1">
+    <row r="27" ht="22.5" hidden="1" customHeight="1">
       <c r="A27" s="8">
         <v>46181.881908958334</v>
       </c>
@@ -1920,7 +1951,7 @@
       </c>
       <c r="AA27" s="11"/>
     </row>
-    <row r="28" ht="22.5" customHeight="1">
+    <row r="28" ht="22.5" hidden="1" customHeight="1">
       <c r="A28" s="8">
         <v>46182.32193653935</v>
       </c>
@@ -1977,7 +2008,7 @@
       </c>
       <c r="AA28" s="11"/>
     </row>
-    <row r="29" ht="22.5" customHeight="1">
+    <row r="29" ht="22.5" hidden="1" customHeight="1">
       <c r="A29" s="8">
         <v>46183.69950311343</v>
       </c>
@@ -2016,7 +2047,7 @@
       </c>
       <c r="AA29" s="11"/>
     </row>
-    <row r="30" ht="22.5" customHeight="1">
+    <row r="30" ht="22.5" hidden="1" customHeight="1">
       <c r="A30" s="8">
         <v>46188.4017772338</v>
       </c>
@@ -2037,7 +2068,7 @@
       </c>
       <c r="AA30" s="11"/>
     </row>
-    <row r="31" ht="22.5" customHeight="1">
+    <row r="31" ht="22.5" hidden="1" customHeight="1">
       <c r="A31" s="8">
         <v>46188.89812909722</v>
       </c>
@@ -2076,7 +2107,7 @@
       </c>
       <c r="AA31" s="11"/>
     </row>
-    <row r="32" ht="22.5" customHeight="1">
+    <row r="32" ht="22.5" hidden="1" customHeight="1">
       <c r="A32" s="8">
         <v>46188.94795862268</v>
       </c>
@@ -2133,7 +2164,7 @@
       </c>
       <c r="AA32" s="11"/>
     </row>
-    <row r="33" ht="22.5" customHeight="1">
+    <row r="33" ht="22.5" hidden="1" customHeight="1">
       <c r="A33" s="8">
         <v>46190.88733893519</v>
       </c>
@@ -2205,7 +2236,7 @@
       </c>
       <c r="AA33" s="11"/>
     </row>
-    <row r="34" ht="22.5" customHeight="1">
+    <row r="34" ht="22.5" hidden="1" customHeight="1">
       <c r="A34" s="8">
         <v>46193.24108553241</v>
       </c>
@@ -2271,7 +2302,7 @@
       </c>
       <c r="AA34" s="11"/>
     </row>
-    <row r="35" ht="22.5" customHeight="1">
+    <row r="35" ht="22.5" hidden="1" customHeight="1">
       <c r="A35" s="8">
         <v>46203.74042241898</v>
       </c>
@@ -2301,7 +2332,7 @@
       </c>
       <c r="AA35" s="11"/>
     </row>
-    <row r="36" ht="22.5" customHeight="1">
+    <row r="36" ht="22.5" hidden="1" customHeight="1">
       <c r="A36" s="8">
         <v>46203.89475577546</v>
       </c>
@@ -2331,7 +2362,7 @@
       </c>
       <c r="AA36" s="11"/>
     </row>
-    <row r="37" ht="22.5" customHeight="1">
+    <row r="37" ht="22.5" hidden="1" customHeight="1">
       <c r="A37" s="8">
         <v>46204.641427002316</v>
       </c>
@@ -2367,7 +2398,7 @@
       </c>
       <c r="AA37" s="11"/>
     </row>
-    <row r="38" ht="22.5" customHeight="1">
+    <row r="38" ht="22.5" hidden="1" customHeight="1">
       <c r="A38" s="8">
         <v>46204.77615667824</v>
       </c>
@@ -2424,7 +2455,7 @@
       </c>
       <c r="AA38" s="11"/>
     </row>
-    <row r="39" ht="22.5" customHeight="1">
+    <row r="39" ht="22.5" hidden="1" customHeight="1">
       <c r="A39" s="8">
         <v>46204.96687071759</v>
       </c>
@@ -2472,7 +2503,7 @@
       </c>
       <c r="AA39" s="11"/>
     </row>
-    <row r="40" ht="22.5" customHeight="1">
+    <row r="40" ht="22.5" hidden="1" customHeight="1">
       <c r="A40" s="8">
         <v>46206.424526874995</v>
       </c>
@@ -2520,7 +2551,7 @@
       </c>
       <c r="AA40" s="11"/>
     </row>
-    <row r="41" ht="22.5" customHeight="1">
+    <row r="41" ht="22.5" hidden="1" customHeight="1">
       <c r="A41" s="8">
         <v>46206.620050046295</v>
       </c>
@@ -2550,7 +2581,7 @@
       </c>
       <c r="AA41" s="11"/>
     </row>
-    <row r="42" ht="22.5" customHeight="1">
+    <row r="42" ht="22.5" hidden="1" customHeight="1">
       <c r="A42" s="8">
         <v>46208.969972384264</v>
       </c>
@@ -2607,7 +2638,7 @@
       </c>
       <c r="AA42" s="11"/>
     </row>
-    <row r="43" ht="22.5" customHeight="1">
+    <row r="43" ht="22.5" hidden="1" customHeight="1">
       <c r="A43" s="8">
         <v>46209.375567870375</v>
       </c>
@@ -2628,7 +2659,7 @@
       </c>
       <c r="AA43" s="11"/>
     </row>
-    <row r="44" ht="22.5" customHeight="1">
+    <row r="44" ht="22.5" hidden="1" customHeight="1">
       <c r="A44" s="8">
         <v>46209.734403078706</v>
       </c>
@@ -2664,7 +2695,7 @@
       </c>
       <c r="AA44" s="11"/>
     </row>
-    <row r="45" ht="22.5" customHeight="1">
+    <row r="45" ht="22.5" hidden="1" customHeight="1">
       <c r="A45" s="8">
         <v>46215.557906319445</v>
       </c>
@@ -2739,7 +2770,7 @@
       </c>
       <c r="AA45" s="11"/>
     </row>
-    <row r="46" ht="22.5" customHeight="1">
+    <row r="46" ht="22.5" hidden="1" customHeight="1">
       <c r="A46" s="8">
         <v>46216.3521159838</v>
       </c>
@@ -2805,7 +2836,7 @@
       </c>
       <c r="AA46" s="11"/>
     </row>
-    <row r="47" ht="22.5" customHeight="1">
+    <row r="47" ht="22.5" hidden="1" customHeight="1">
       <c r="A47" s="8">
         <v>46216.69194454861</v>
       </c>
@@ -2862,7 +2893,7 @@
       </c>
       <c r="AA47" s="11"/>
     </row>
-    <row r="48" ht="22.5" customHeight="1">
+    <row r="48" ht="22.5" hidden="1" customHeight="1">
       <c r="A48" s="8">
         <v>46216.92590599537</v>
       </c>
@@ -2910,7 +2941,7 @@
       </c>
       <c r="AA48" s="11"/>
     </row>
-    <row r="49" ht="22.5" customHeight="1">
+    <row r="49" ht="22.5" hidden="1" customHeight="1">
       <c r="A49" s="8">
         <v>46217.47602858796</v>
       </c>
@@ -2958,7 +2989,7 @@
       </c>
       <c r="AA49" s="11"/>
     </row>
-    <row r="50" ht="22.5" customHeight="1">
+    <row r="50" ht="22.5" hidden="1" customHeight="1">
       <c r="A50" s="8">
         <v>46217.9430246875</v>
       </c>
@@ -3024,7 +3055,7 @@
       </c>
       <c r="AA50" s="11"/>
     </row>
-    <row r="51" ht="22.5" customHeight="1">
+    <row r="51" ht="22.5" hidden="1" customHeight="1">
       <c r="A51" s="8">
         <v>46219.84970673611</v>
       </c>
@@ -3045,7 +3076,7 @@
       </c>
       <c r="AA51" s="11"/>
     </row>
-    <row r="52" ht="22.5" customHeight="1">
+    <row r="52" ht="22.5" hidden="1" customHeight="1">
       <c r="A52" s="8">
         <v>46220.77317190972</v>
       </c>
@@ -3102,7 +3133,7 @@
       </c>
       <c r="AA52" s="11"/>
     </row>
-    <row r="53" ht="22.5" customHeight="1">
+    <row r="53" ht="22.5" hidden="1" customHeight="1">
       <c r="A53" s="8">
         <v>46220.782720752315</v>
       </c>
@@ -3177,7 +3208,7 @@
       </c>
       <c r="AA53" s="11"/>
     </row>
-    <row r="54" ht="22.5" customHeight="1">
+    <row r="54" ht="22.5" hidden="1" customHeight="1">
       <c r="A54" s="8">
         <v>46222.7757115625</v>
       </c>
@@ -3252,7 +3283,7 @@
       </c>
       <c r="AA54" s="11"/>
     </row>
-    <row r="55" ht="22.5" customHeight="1">
+    <row r="55" ht="22.5" hidden="1" customHeight="1">
       <c r="A55" s="8">
         <v>46223.36424023148</v>
       </c>
@@ -3276,7 +3307,7 @@
       </c>
       <c r="AA55" s="11"/>
     </row>
-    <row r="56" ht="22.5" customHeight="1">
+    <row r="56" ht="22.5" hidden="1" customHeight="1">
       <c r="A56" s="8">
         <v>46223.79855170139</v>
       </c>
@@ -3351,7 +3382,7 @@
       </c>
       <c r="AA56" s="11"/>
     </row>
-    <row r="57" ht="22.5" customHeight="1">
+    <row r="57" ht="22.5" hidden="1" customHeight="1">
       <c r="A57" s="8">
         <v>46235.618820648146</v>
       </c>
@@ -3390,7 +3421,7 @@
       </c>
       <c r="AA57" s="11"/>
     </row>
-    <row r="58" ht="22.5" customHeight="1">
+    <row r="58" ht="22.5" hidden="1" customHeight="1">
       <c r="A58" s="8">
         <v>46236.859332569446</v>
       </c>
@@ -3420,7 +3451,7 @@
       </c>
       <c r="AA58" s="11"/>
     </row>
-    <row r="59" ht="22.5" customHeight="1">
+    <row r="59" ht="22.5" hidden="1" customHeight="1">
       <c r="A59" s="8">
         <v>46239.707476006944</v>
       </c>
@@ -3453,7 +3484,7 @@
       </c>
       <c r="AA59" s="11"/>
     </row>
-    <row r="60" ht="22.5" customHeight="1">
+    <row r="60" ht="22.5" hidden="1" customHeight="1">
       <c r="A60" s="8">
         <v>46239.79803805555</v>
       </c>
@@ -3510,7 +3541,7 @@
       </c>
       <c r="AA60" s="11"/>
     </row>
-    <row r="61" ht="22.5" customHeight="1">
+    <row r="61" ht="22.5" hidden="1" customHeight="1">
       <c r="A61" s="8">
         <v>46239.82072309028</v>
       </c>
@@ -3546,7 +3577,7 @@
       </c>
       <c r="AA61" s="11"/>
     </row>
-    <row r="62" ht="22.5" customHeight="1">
+    <row r="62" ht="22.5" hidden="1" customHeight="1">
       <c r="A62" s="8">
         <v>46241.55575290509</v>
       </c>
@@ -3608,7 +3639,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="63" ht="22.5" customHeight="1">
+    <row r="63" ht="22.5" hidden="1" customHeight="1">
       <c r="A63" s="8">
         <v>46241.71240017361</v>
       </c>
@@ -3682,7 +3713,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="64" ht="22.5" customHeight="1">
+    <row r="64" ht="22.5" hidden="1" customHeight="1">
       <c r="A64" s="8">
         <v>46242.65253738426</v>
       </c>
@@ -3711,7 +3742,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="65" ht="22.5" customHeight="1">
+    <row r="65" ht="22.5" hidden="1" customHeight="1">
       <c r="A65" s="8">
         <v>46243.3566297338</v>
       </c>
@@ -3758,7 +3789,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="66" ht="22.5" customHeight="1">
+    <row r="66" ht="22.5" hidden="1" customHeight="1">
       <c r="A66" s="8">
         <v>46243.69412138889</v>
       </c>
@@ -3793,7 +3824,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="67" ht="22.5" customHeight="1">
+    <row r="67" ht="22.5" hidden="1" customHeight="1">
       <c r="A67" s="8">
         <v>46244.65016612269</v>
       </c>
@@ -3858,7 +3889,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="68" ht="22.5" customHeight="1">
+    <row r="68" ht="22.5" hidden="1" customHeight="1">
       <c r="A68" s="8">
         <v>46244.6941922338</v>
       </c>
@@ -3878,7 +3909,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="69" ht="22.5" customHeight="1">
+    <row r="69" ht="22.5" hidden="1" customHeight="1">
       <c r="A69" s="8">
         <v>46244.702560300924</v>
       </c>
@@ -4037,6 +4068,1247 @@
       </c>
       <c r="Z72" s="10" t="s">
         <v>85</v>
+      </c>
+    </row>
+    <row r="73" ht="22.5" hidden="1" customHeight="1">
+      <c r="A73" s="8">
+        <v>46251.77397138889</v>
+      </c>
+      <c r="B73" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C73" s="10">
+        <v>2026.0</v>
+      </c>
+      <c r="D73" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="E73" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="H73" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="I73" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="J73" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="K73" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="L73" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="M73" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="N73" s="10">
+        <v>3.0</v>
+      </c>
+      <c r="O73" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="P73" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="Q73" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="R73" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="S73" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="T73" s="10">
+        <v>2.0</v>
+      </c>
+      <c r="U73" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="V73" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="W73" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="X73" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="Y73" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="Z73" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="74" ht="22.5" customHeight="1">
+      <c r="A74" s="8">
+        <v>46251.7789425</v>
+      </c>
+      <c r="B74" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="C74" s="10">
+        <v>2026.0</v>
+      </c>
+      <c r="D74" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="E74" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H74" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="I74" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="J74" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="K74" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="L74" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="M74" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="N74" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O74" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="P74" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="Q74" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="R74" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="S74" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="T74" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="U74" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="V74" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="W74" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="X74" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="Y74" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="Z74" s="10" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="75" ht="22.5" hidden="1" customHeight="1">
+      <c r="A75" s="8">
+        <v>46252.27823043981</v>
+      </c>
+      <c r="B75" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C75" s="10">
+        <v>2026.0</v>
+      </c>
+      <c r="D75" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="E75" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="K75" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="L75" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="M75" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="Z75" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="76" ht="22.5" hidden="1" customHeight="1">
+      <c r="A76" s="8">
+        <v>46257.441359282406</v>
+      </c>
+      <c r="B76" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C76" s="10">
+        <v>2026.0</v>
+      </c>
+      <c r="D76" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="E76" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="K76" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="L76" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="M76" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="N76" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="P76" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z76" s="10" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="77" ht="22.5" hidden="1" customHeight="1">
+      <c r="A77" s="8">
+        <v>46258.5101271875</v>
+      </c>
+      <c r="B77" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C77" s="10">
+        <v>2026.0</v>
+      </c>
+      <c r="D77" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F77" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H77" s="10">
+        <v>7.0</v>
+      </c>
+      <c r="I77" s="10">
+        <v>6.0</v>
+      </c>
+      <c r="J77" s="10">
+        <v>5.0</v>
+      </c>
+      <c r="K77" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="L77" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="M77" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="N77" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O77" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="P77" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="Q77" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="R77" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="S77" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="T77" s="10">
+        <v>2.0</v>
+      </c>
+      <c r="U77" s="10">
+        <v>4.0</v>
+      </c>
+      <c r="V77" s="10">
+        <v>4.0</v>
+      </c>
+      <c r="Z77" s="10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="78" ht="22.5" customHeight="1">
+      <c r="A78" s="8">
+        <v>46265.800786064814</v>
+      </c>
+      <c r="B78" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="C78" s="10">
+        <v>2026.0</v>
+      </c>
+      <c r="D78" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="G78" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="H78" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="I78" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="L78" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="N78" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="O78" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="R78" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="T78" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="U78" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z78" s="10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="79" ht="22.5" customHeight="1">
+      <c r="A79" s="8">
+        <v>46266.479768749996</v>
+      </c>
+      <c r="B79" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="C79" s="10">
+        <v>2026.0</v>
+      </c>
+      <c r="D79" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="G79" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="K79" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="L79" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="M79" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="N79" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="O79" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="P79" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="Z79" s="10" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="80" ht="22.5" customHeight="1">
+      <c r="A80" s="8">
+        <v>46266.81808168982</v>
+      </c>
+      <c r="B80" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="C80" s="10">
+        <v>2026.0</v>
+      </c>
+      <c r="D80" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="G80" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="H80" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="I80" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="J80" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="Z80" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="81" ht="22.5" customHeight="1">
+      <c r="A81" s="8">
+        <v>46268.51575239583</v>
+      </c>
+      <c r="B81" s="10">
+        <v>8.0</v>
+      </c>
+      <c r="C81" s="10">
+        <v>2026.0</v>
+      </c>
+      <c r="D81" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="E81" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="H81" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="I81" s="10">
+        <v>3.0</v>
+      </c>
+      <c r="J81" s="10">
+        <v>33.0</v>
+      </c>
+      <c r="Z81" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="82" ht="22.5" customHeight="1">
+      <c r="A82" s="8">
+        <v>46269.61522895833</v>
+      </c>
+      <c r="B82" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="C82" s="10">
+        <v>2026.0</v>
+      </c>
+      <c r="D82" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="G82" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="H82" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="W82" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="X82" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="Z82" s="10" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="83" ht="22.5" customHeight="1">
+      <c r="A83" s="8">
+        <v>46271.919671550924</v>
+      </c>
+      <c r="B83" s="10">
+        <v>8.0</v>
+      </c>
+      <c r="C83" s="10">
+        <v>2026.0</v>
+      </c>
+      <c r="D83" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F83" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="H83" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="I83" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="J83" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="K83" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="L83" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="M83" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="N83" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O83" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="P83" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="Q83" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="R83" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="S83" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="T83" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="U83" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="V83" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="W83" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="X83" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="Y83" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="Z83" s="10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="84" ht="22.5" customHeight="1">
+      <c r="A84" s="8">
+        <v>46272.875376655094</v>
+      </c>
+      <c r="B84" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="C84" s="10">
+        <v>2026.0</v>
+      </c>
+      <c r="D84" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="G84" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="H84" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="I84" s="10">
+        <v>13.0</v>
+      </c>
+      <c r="J84" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="Z84" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="85" ht="22.5" hidden="1" customHeight="1">
+      <c r="A85" s="8">
+        <v>46273.591041747684</v>
+      </c>
+      <c r="B85" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C85" s="10">
+        <v>2026.0</v>
+      </c>
+      <c r="D85" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="G85" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="H85" s="10">
+        <v>2.0</v>
+      </c>
+      <c r="I85" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="W85" s="10">
+        <v>3.0</v>
+      </c>
+      <c r="X85" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="Y85" s="10">
+        <v>15.0</v>
+      </c>
+      <c r="Z85" s="10" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="86" ht="22.5" customHeight="1">
+      <c r="A86" s="8">
+        <v>46273.74572407408</v>
+      </c>
+      <c r="B86" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="C86" s="10">
+        <v>2026.0</v>
+      </c>
+      <c r="D86" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="E86" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="K86" s="10">
+        <v>2.0</v>
+      </c>
+      <c r="L86" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="M86" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="N86" s="10">
+        <v>3.0</v>
+      </c>
+      <c r="O86" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="P86" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="Z86" s="10" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="87" ht="22.5" customHeight="1">
+      <c r="A87" s="8">
+        <v>46274.36138298611</v>
+      </c>
+      <c r="B87" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="C87" s="10">
+        <v>2026.0</v>
+      </c>
+      <c r="D87" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="G87" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q87" s="10">
+        <v>9.0</v>
+      </c>
+      <c r="R87" s="10">
+        <v>5.0</v>
+      </c>
+      <c r="Z87" s="10" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="88" ht="22.5" customHeight="1">
+      <c r="A88" s="8">
+        <v>46274.499461203704</v>
+      </c>
+      <c r="B88" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="C88" s="10">
+        <v>2026.0</v>
+      </c>
+      <c r="D88" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="G88" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="H88" s="10">
+        <v>4.0</v>
+      </c>
+      <c r="J88" s="10">
+        <v>6.0</v>
+      </c>
+      <c r="L88" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="M88" s="10">
+        <v>2.0</v>
+      </c>
+      <c r="N88" s="10">
+        <v>3.0</v>
+      </c>
+      <c r="P88" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="V88" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="Z88" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="89" ht="22.5" customHeight="1">
+      <c r="A89" s="8">
+        <v>46274.8280094213</v>
+      </c>
+      <c r="B89" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="C89" s="10">
+        <v>2026.0</v>
+      </c>
+      <c r="D89" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="E89" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="H89" s="10">
+        <v>4.0</v>
+      </c>
+      <c r="J89" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="K89" s="10">
+        <v>3.0</v>
+      </c>
+      <c r="L89" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="M89" s="10">
+        <v>2.0</v>
+      </c>
+      <c r="N89" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O89" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="P89" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="Q89" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="R89" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="S89" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="T89" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="U89" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="V89" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="W89" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="X89" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="Y89" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="Z89" s="10" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="90" ht="22.5" customHeight="1">
+      <c r="A90" s="8">
+        <v>46274.82950299769</v>
+      </c>
+      <c r="B90" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="C90" s="10">
+        <v>2026.0</v>
+      </c>
+      <c r="D90" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="G90" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="K90" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="L90" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M90" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="N90" s="10">
+        <v>14.0</v>
+      </c>
+      <c r="O90" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="P90" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="Z90" s="10" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="91" ht="22.5" customHeight="1">
+      <c r="A91" s="8">
+        <v>46274.88633732639</v>
+      </c>
+      <c r="B91" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="C91" s="10">
+        <v>2026.0</v>
+      </c>
+      <c r="D91" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F91" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="H91" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="I91" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="J91" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="K91" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="L91" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="M91" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="N91" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O91" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="P91" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="Q91" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="R91" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="S91" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="Z91" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="92" ht="22.5" customHeight="1">
+      <c r="A92" s="8">
+        <v>46275.36955942129</v>
+      </c>
+      <c r="B92" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="C92" s="10">
+        <v>2026.0</v>
+      </c>
+      <c r="D92" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F92" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="Z92" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="93" ht="22.5" customHeight="1">
+      <c r="A93" s="8">
+        <v>46275.416913761575</v>
+      </c>
+      <c r="B93" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="C93" s="10">
+        <v>2026.0</v>
+      </c>
+      <c r="D93" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="E93" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="H93" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="I93" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="J93" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="K93" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="L93" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="M93" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="Q93" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="R93" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="S93" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="T93" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="U93" s="10">
+        <v>4.0</v>
+      </c>
+      <c r="V93" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="Z93" s="10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="94" ht="22.5" hidden="1" customHeight="1">
+      <c r="A94" s="8">
+        <v>46275.42604790509</v>
+      </c>
+      <c r="B94" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="C94" s="10">
+        <v>2026.0</v>
+      </c>
+      <c r="D94" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="G94" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="O94" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="P94" s="10">
+        <v>4.0</v>
+      </c>
+      <c r="Z94" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="95" ht="22.5" customHeight="1">
+      <c r="A95" s="8">
+        <v>46275.65150252315</v>
+      </c>
+      <c r="B95" s="10">
+        <v>8.0</v>
+      </c>
+      <c r="C95" s="10">
+        <v>2026.0</v>
+      </c>
+      <c r="D95" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F95" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="H95" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="I95" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="J95" s="10">
+        <v>2.0</v>
+      </c>
+      <c r="K95" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="L95" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="M95" s="10">
+        <v>8.0</v>
+      </c>
+      <c r="Q95" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="R95" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="S95" s="10">
+        <v>10.0</v>
+      </c>
+      <c r="Z95" s="10" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="96" ht="22.5" customHeight="1">
+      <c r="A96" s="8">
+        <v>46275.71898621527</v>
+      </c>
+      <c r="B96" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="C96" s="10">
+        <v>2026.0</v>
+      </c>
+      <c r="D96" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="G96" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="H96" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="I96" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="J96" s="10">
+        <v>7.0</v>
+      </c>
+      <c r="K96" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="L96" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="M96" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="N96" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O96" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="P96" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="Q96" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="R96" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="S96" s="10">
+        <v>14.0</v>
+      </c>
+      <c r="W96" s="10">
+        <v>2.0</v>
+      </c>
+      <c r="X96" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="Y96" s="10">
+        <v>16.0</v>
+      </c>
+      <c r="Z96" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="97" ht="22.5" customHeight="1">
+      <c r="A97" s="8">
+        <v>46275.77731983796</v>
+      </c>
+      <c r="B97" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="C97" s="10">
+        <v>2026.0</v>
+      </c>
+      <c r="D97" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="E97" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="H97" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="I97" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="J97" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="K97" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="L97" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="M97" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="N97" s="10">
+        <v>2.0</v>
+      </c>
+      <c r="O97" s="10">
+        <v>2.0</v>
+      </c>
+      <c r="P97" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="T97" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="U97" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="V97" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="Z97" s="10" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="98" ht="22.5" hidden="1" customHeight="1">
+      <c r="A98" s="8">
+        <v>46277.80482196759</v>
+      </c>
+      <c r="B98" s="10">
+        <v>7.0</v>
+      </c>
+      <c r="C98" s="10">
+        <v>2026.0</v>
+      </c>
+      <c r="D98" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="G98" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z98" s="10" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="99" ht="22.5" customHeight="1">
+      <c r="A99" s="8">
+        <v>46277.80555396991</v>
+      </c>
+      <c r="B99" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="C99" s="10">
+        <v>2026.0</v>
+      </c>
+      <c r="D99" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="G99" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="M99" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="Z99" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="100" ht="22.5" customHeight="1">
+      <c r="A100" s="8">
+        <v>46279.60584042824</v>
+      </c>
+      <c r="B100" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="C100" s="10">
+        <v>2026.0</v>
+      </c>
+      <c r="D100" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="E100" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="H100" s="10">
+        <v>3.0</v>
+      </c>
+      <c r="I100" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="J100" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="K100" s="10">
+        <v>2.0</v>
+      </c>
+      <c r="L100" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="M100" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="N100" s="10">
+        <v>2.0</v>
+      </c>
+      <c r="O100" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="P100" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="Q100" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="R100" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="S100" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="T100" s="10">
+        <v>8.0</v>
+      </c>
+      <c r="U100" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="V100" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="W100" s="10">
+        <v>1.0</v>
+      </c>
+      <c r="X100" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="Y100" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="Z100" s="10" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/FORMULÁRIO QUALITATIVO 2026 (respostas).xlsx
+++ b/FORMULÁRIO QUALITATIVO 2026 (respostas).xlsx
@@ -6,14 +6,14 @@
     <sheet state="visible" name="Respostas ao formulário 1" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'Respostas ao formulário 1'!$A$1:$AA$100</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'Respostas ao formulário 1'!$A$1:$AA$101</definedName>
   </definedNames>
   <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="94">
   <si>
     <t>Carimbo de data/hora</t>
   </si>
@@ -447,15 +447,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:AA100" displayName="Form_Responses" name="Form_Responses" id="1">
-  <autoFilter ref="$A$1:$AA$100">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="08"/>
-        <filter val="8"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:AA101" displayName="Form_Responses" name="Form_Responses" id="1">
+  <autoFilter ref="$A$1:$AA$101"/>
   <tableColumns count="27">
     <tableColumn name="Carimbo de data/hora" id="1"/>
     <tableColumn name="MÊS" id="2"/>
@@ -793,7 +786,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" ht="22.5" hidden="1" customHeight="1">
+    <row r="2" ht="22.5" customHeight="1">
       <c r="A2" s="3">
         <v>46161.66699090278</v>
       </c>
@@ -870,7 +863,7 @@
       </c>
       <c r="AA2" s="7"/>
     </row>
-    <row r="3" ht="22.5" hidden="1" customHeight="1">
+    <row r="3" ht="22.5" customHeight="1">
       <c r="A3" s="3">
         <v>46161.717658842594</v>
       </c>
@@ -947,7 +940,7 @@
       </c>
       <c r="AA3" s="7"/>
     </row>
-    <row r="4" ht="22.5" hidden="1" customHeight="1">
+    <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="3">
         <v>46162.32503172454</v>
       </c>
@@ -1012,7 +1005,7 @@
       </c>
       <c r="AA4" s="7"/>
     </row>
-    <row r="5" ht="22.5" hidden="1" customHeight="1">
+    <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="3">
         <v>46162.49362635417</v>
       </c>
@@ -1057,7 +1050,7 @@
       </c>
       <c r="AA5" s="7"/>
     </row>
-    <row r="6" ht="22.5" hidden="1" customHeight="1">
+    <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="3">
         <v>46162.55207898148</v>
       </c>
@@ -1102,7 +1095,7 @@
       </c>
       <c r="AA6" s="7"/>
     </row>
-    <row r="7" ht="22.5" hidden="1" customHeight="1">
+    <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="3">
         <v>46165.76160042824</v>
       </c>
@@ -1159,7 +1152,7 @@
       </c>
       <c r="AA7" s="7"/>
     </row>
-    <row r="8" ht="22.5" hidden="1" customHeight="1">
+    <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="8">
         <v>46168.36660253472</v>
       </c>
@@ -1207,7 +1200,7 @@
       </c>
       <c r="AA8" s="11"/>
     </row>
-    <row r="9" ht="22.5" hidden="1" customHeight="1">
+    <row r="9" ht="22.5" customHeight="1">
       <c r="A9" s="8">
         <v>46169.744550648145</v>
       </c>
@@ -1282,7 +1275,7 @@
       </c>
       <c r="AA9" s="11"/>
     </row>
-    <row r="10" ht="22.5" hidden="1" customHeight="1">
+    <row r="10" ht="22.5" customHeight="1">
       <c r="A10" s="8">
         <v>46169.90514916666</v>
       </c>
@@ -1357,7 +1350,7 @@
       </c>
       <c r="AA10" s="11"/>
     </row>
-    <row r="11" ht="22.5" hidden="1" customHeight="1">
+    <row r="11" ht="22.5" customHeight="1">
       <c r="A11" s="8">
         <v>46172.67972921296</v>
       </c>
@@ -1378,7 +1371,7 @@
       </c>
       <c r="AA11" s="11"/>
     </row>
-    <row r="12" ht="22.5" hidden="1" customHeight="1">
+    <row r="12" ht="22.5" customHeight="1">
       <c r="A12" s="8">
         <v>46172.697124618055</v>
       </c>
@@ -1435,7 +1428,7 @@
       </c>
       <c r="AA12" s="11"/>
     </row>
-    <row r="13" ht="22.5" hidden="1" customHeight="1">
+    <row r="13" ht="22.5" customHeight="1">
       <c r="A13" s="8">
         <v>46172.7069606713</v>
       </c>
@@ -1462,7 +1455,7 @@
       </c>
       <c r="AA13" s="11"/>
     </row>
-    <row r="14" ht="22.5" hidden="1" customHeight="1">
+    <row r="14" ht="22.5" customHeight="1">
       <c r="A14" s="8">
         <v>46172.70767744213</v>
       </c>
@@ -1486,7 +1479,7 @@
       </c>
       <c r="AA14" s="11"/>
     </row>
-    <row r="15" ht="22.5" hidden="1" customHeight="1">
+    <row r="15" ht="22.5" customHeight="1">
       <c r="A15" s="8">
         <v>46172.7086074074</v>
       </c>
@@ -1519,7 +1512,7 @@
       </c>
       <c r="AA15" s="11"/>
     </row>
-    <row r="16" ht="22.5" hidden="1" customHeight="1">
+    <row r="16" ht="22.5" customHeight="1">
       <c r="A16" s="8">
         <v>46173.51154100694</v>
       </c>
@@ -1549,7 +1542,7 @@
       </c>
       <c r="AA16" s="11"/>
     </row>
-    <row r="17" ht="22.5" hidden="1" customHeight="1">
+    <row r="17" ht="22.5" customHeight="1">
       <c r="A17" s="8">
         <v>46173.86278575231</v>
       </c>
@@ -1576,7 +1569,7 @@
       </c>
       <c r="AA17" s="11"/>
     </row>
-    <row r="18" ht="22.5" hidden="1" customHeight="1">
+    <row r="18" ht="22.5" customHeight="1">
       <c r="A18" s="8">
         <v>46174.63476946759</v>
       </c>
@@ -1606,7 +1599,7 @@
       </c>
       <c r="AA18" s="11"/>
     </row>
-    <row r="19" ht="22.5" hidden="1" customHeight="1">
+    <row r="19" ht="22.5" customHeight="1">
       <c r="A19" s="8">
         <v>46174.66969215278</v>
       </c>
@@ -1672,7 +1665,7 @@
       </c>
       <c r="AA19" s="11"/>
     </row>
-    <row r="20" ht="22.5" hidden="1" customHeight="1">
+    <row r="20" ht="22.5" customHeight="1">
       <c r="A20" s="8">
         <v>46174.74549342593</v>
       </c>
@@ -1729,7 +1722,7 @@
       </c>
       <c r="AA20" s="11"/>
     </row>
-    <row r="21" ht="22.5" hidden="1" customHeight="1">
+    <row r="21" ht="22.5" customHeight="1">
       <c r="A21" s="8">
         <v>46176.80739381944</v>
       </c>
@@ -1771,7 +1764,7 @@
       </c>
       <c r="AA21" s="11"/>
     </row>
-    <row r="22" ht="22.5" hidden="1" customHeight="1">
+    <row r="22" ht="22.5" customHeight="1">
       <c r="A22" s="8">
         <v>46178.44168116898</v>
       </c>
@@ -1810,7 +1803,7 @@
       </c>
       <c r="AA22" s="11"/>
     </row>
-    <row r="23" ht="22.5" hidden="1" customHeight="1">
+    <row r="23" ht="22.5" customHeight="1">
       <c r="A23" s="8">
         <v>46179.84200296296</v>
       </c>
@@ -1840,7 +1833,7 @@
       </c>
       <c r="AA23" s="11"/>
     </row>
-    <row r="24" ht="22.5" hidden="1" customHeight="1">
+    <row r="24" ht="22.5" customHeight="1">
       <c r="A24" s="8">
         <v>46181.528076828705</v>
       </c>
@@ -1861,7 +1854,7 @@
       </c>
       <c r="AA24" s="11"/>
     </row>
-    <row r="25" ht="22.5" hidden="1" customHeight="1">
+    <row r="25" ht="22.5" customHeight="1">
       <c r="A25" s="8">
         <v>46181.86944918981</v>
       </c>
@@ -1891,7 +1884,7 @@
       </c>
       <c r="AA25" s="11"/>
     </row>
-    <row r="26" ht="22.5" hidden="1" customHeight="1">
+    <row r="26" ht="22.5" customHeight="1">
       <c r="A26" s="8">
         <v>46181.870301689814</v>
       </c>
@@ -1921,7 +1914,7 @@
       </c>
       <c r="AA26" s="11"/>
     </row>
-    <row r="27" ht="22.5" hidden="1" customHeight="1">
+    <row r="27" ht="22.5" customHeight="1">
       <c r="A27" s="8">
         <v>46181.881908958334</v>
       </c>
@@ -1951,7 +1944,7 @@
       </c>
       <c r="AA27" s="11"/>
     </row>
-    <row r="28" ht="22.5" hidden="1" customHeight="1">
+    <row r="28" ht="22.5" customHeight="1">
       <c r="A28" s="8">
         <v>46182.32193653935</v>
       </c>
@@ -2008,7 +2001,7 @@
       </c>
       <c r="AA28" s="11"/>
     </row>
-    <row r="29" ht="22.5" hidden="1" customHeight="1">
+    <row r="29" ht="22.5" customHeight="1">
       <c r="A29" s="8">
         <v>46183.69950311343</v>
       </c>
@@ -2047,7 +2040,7 @@
       </c>
       <c r="AA29" s="11"/>
     </row>
-    <row r="30" ht="22.5" hidden="1" customHeight="1">
+    <row r="30" ht="22.5" customHeight="1">
       <c r="A30" s="8">
         <v>46188.4017772338</v>
       </c>
@@ -2068,7 +2061,7 @@
       </c>
       <c r="AA30" s="11"/>
     </row>
-    <row r="31" ht="22.5" hidden="1" customHeight="1">
+    <row r="31" ht="22.5" customHeight="1">
       <c r="A31" s="8">
         <v>46188.89812909722</v>
       </c>
@@ -2107,7 +2100,7 @@
       </c>
       <c r="AA31" s="11"/>
     </row>
-    <row r="32" ht="22.5" hidden="1" customHeight="1">
+    <row r="32" ht="22.5" customHeight="1">
       <c r="A32" s="8">
         <v>46188.94795862268</v>
       </c>
@@ -2164,7 +2157,7 @@
       </c>
       <c r="AA32" s="11"/>
     </row>
-    <row r="33" ht="22.5" hidden="1" customHeight="1">
+    <row r="33" ht="22.5" customHeight="1">
       <c r="A33" s="8">
         <v>46190.88733893519</v>
       </c>
@@ -2236,7 +2229,7 @@
       </c>
       <c r="AA33" s="11"/>
     </row>
-    <row r="34" ht="22.5" hidden="1" customHeight="1">
+    <row r="34" ht="22.5" customHeight="1">
       <c r="A34" s="8">
         <v>46193.24108553241</v>
       </c>
@@ -2302,7 +2295,7 @@
       </c>
       <c r="AA34" s="11"/>
     </row>
-    <row r="35" ht="22.5" hidden="1" customHeight="1">
+    <row r="35" ht="22.5" customHeight="1">
       <c r="A35" s="8">
         <v>46203.74042241898</v>
       </c>
@@ -2332,7 +2325,7 @@
       </c>
       <c r="AA35" s="11"/>
     </row>
-    <row r="36" ht="22.5" hidden="1" customHeight="1">
+    <row r="36" ht="22.5" customHeight="1">
       <c r="A36" s="8">
         <v>46203.89475577546</v>
       </c>
@@ -2362,7 +2355,7 @@
       </c>
       <c r="AA36" s="11"/>
     </row>
-    <row r="37" ht="22.5" hidden="1" customHeight="1">
+    <row r="37" ht="22.5" customHeight="1">
       <c r="A37" s="8">
         <v>46204.641427002316</v>
       </c>
@@ -2398,7 +2391,7 @@
       </c>
       <c r="AA37" s="11"/>
     </row>
-    <row r="38" ht="22.5" hidden="1" customHeight="1">
+    <row r="38" ht="22.5" customHeight="1">
       <c r="A38" s="8">
         <v>46204.77615667824</v>
       </c>
@@ -2455,7 +2448,7 @@
       </c>
       <c r="AA38" s="11"/>
     </row>
-    <row r="39" ht="22.5" hidden="1" customHeight="1">
+    <row r="39" ht="22.5" customHeight="1">
       <c r="A39" s="8">
         <v>46204.96687071759</v>
       </c>
@@ -2503,7 +2496,7 @@
       </c>
       <c r="AA39" s="11"/>
     </row>
-    <row r="40" ht="22.5" hidden="1" customHeight="1">
+    <row r="40" ht="22.5" customHeight="1">
       <c r="A40" s="8">
         <v>46206.424526874995</v>
       </c>
@@ -2551,7 +2544,7 @@
       </c>
       <c r="AA40" s="11"/>
     </row>
-    <row r="41" ht="22.5" hidden="1" customHeight="1">
+    <row r="41" ht="22.5" customHeight="1">
       <c r="A41" s="8">
         <v>46206.620050046295</v>
       </c>
@@ -2581,7 +2574,7 @@
       </c>
       <c r="AA41" s="11"/>
     </row>
-    <row r="42" ht="22.5" hidden="1" customHeight="1">
+    <row r="42" ht="22.5" customHeight="1">
       <c r="A42" s="8">
         <v>46208.969972384264</v>
       </c>
@@ -2638,7 +2631,7 @@
       </c>
       <c r="AA42" s="11"/>
     </row>
-    <row r="43" ht="22.5" hidden="1" customHeight="1">
+    <row r="43" ht="22.5" customHeight="1">
       <c r="A43" s="8">
         <v>46209.375567870375</v>
       </c>
@@ -2659,7 +2652,7 @@
       </c>
       <c r="AA43" s="11"/>
     </row>
-    <row r="44" ht="22.5" hidden="1" customHeight="1">
+    <row r="44" ht="22.5" customHeight="1">
       <c r="A44" s="8">
         <v>46209.734403078706</v>
       </c>
@@ -2695,7 +2688,7 @@
       </c>
       <c r="AA44" s="11"/>
     </row>
-    <row r="45" ht="22.5" hidden="1" customHeight="1">
+    <row r="45" ht="22.5" customHeight="1">
       <c r="A45" s="8">
         <v>46215.557906319445</v>
       </c>
@@ -2770,7 +2763,7 @@
       </c>
       <c r="AA45" s="11"/>
     </row>
-    <row r="46" ht="22.5" hidden="1" customHeight="1">
+    <row r="46" ht="22.5" customHeight="1">
       <c r="A46" s="8">
         <v>46216.3521159838</v>
       </c>
@@ -2836,7 +2829,7 @@
       </c>
       <c r="AA46" s="11"/>
     </row>
-    <row r="47" ht="22.5" hidden="1" customHeight="1">
+    <row r="47" ht="22.5" customHeight="1">
       <c r="A47" s="8">
         <v>46216.69194454861</v>
       </c>
@@ -2893,7 +2886,7 @@
       </c>
       <c r="AA47" s="11"/>
     </row>
-    <row r="48" ht="22.5" hidden="1" customHeight="1">
+    <row r="48" ht="22.5" customHeight="1">
       <c r="A48" s="8">
         <v>46216.92590599537</v>
       </c>
@@ -2941,7 +2934,7 @@
       </c>
       <c r="AA48" s="11"/>
     </row>
-    <row r="49" ht="22.5" hidden="1" customHeight="1">
+    <row r="49" ht="22.5" customHeight="1">
       <c r="A49" s="8">
         <v>46217.47602858796</v>
       </c>
@@ -2989,7 +2982,7 @@
       </c>
       <c r="AA49" s="11"/>
     </row>
-    <row r="50" ht="22.5" hidden="1" customHeight="1">
+    <row r="50" ht="22.5" customHeight="1">
       <c r="A50" s="8">
         <v>46217.9430246875</v>
       </c>
@@ -3055,7 +3048,7 @@
       </c>
       <c r="AA50" s="11"/>
     </row>
-    <row r="51" ht="22.5" hidden="1" customHeight="1">
+    <row r="51" ht="22.5" customHeight="1">
       <c r="A51" s="8">
         <v>46219.84970673611</v>
       </c>
@@ -3076,7 +3069,7 @@
       </c>
       <c r="AA51" s="11"/>
     </row>
-    <row r="52" ht="22.5" hidden="1" customHeight="1">
+    <row r="52" ht="22.5" customHeight="1">
       <c r="A52" s="8">
         <v>46220.77317190972</v>
       </c>
@@ -3133,7 +3126,7 @@
       </c>
       <c r="AA52" s="11"/>
     </row>
-    <row r="53" ht="22.5" hidden="1" customHeight="1">
+    <row r="53" ht="22.5" customHeight="1">
       <c r="A53" s="8">
         <v>46220.782720752315</v>
       </c>
@@ -3208,7 +3201,7 @@
       </c>
       <c r="AA53" s="11"/>
     </row>
-    <row r="54" ht="22.5" hidden="1" customHeight="1">
+    <row r="54" ht="22.5" customHeight="1">
       <c r="A54" s="8">
         <v>46222.7757115625</v>
       </c>
@@ -3283,7 +3276,7 @@
       </c>
       <c r="AA54" s="11"/>
     </row>
-    <row r="55" ht="22.5" hidden="1" customHeight="1">
+    <row r="55" ht="22.5" customHeight="1">
       <c r="A55" s="8">
         <v>46223.36424023148</v>
       </c>
@@ -3307,7 +3300,7 @@
       </c>
       <c r="AA55" s="11"/>
     </row>
-    <row r="56" ht="22.5" hidden="1" customHeight="1">
+    <row r="56" ht="22.5" customHeight="1">
       <c r="A56" s="8">
         <v>46223.79855170139</v>
       </c>
@@ -3382,7 +3375,7 @@
       </c>
       <c r="AA56" s="11"/>
     </row>
-    <row r="57" ht="22.5" hidden="1" customHeight="1">
+    <row r="57" ht="22.5" customHeight="1">
       <c r="A57" s="8">
         <v>46235.618820648146</v>
       </c>
@@ -3421,7 +3414,7 @@
       </c>
       <c r="AA57" s="11"/>
     </row>
-    <row r="58" ht="22.5" hidden="1" customHeight="1">
+    <row r="58" ht="22.5" customHeight="1">
       <c r="A58" s="8">
         <v>46236.859332569446</v>
       </c>
@@ -3451,7 +3444,7 @@
       </c>
       <c r="AA58" s="11"/>
     </row>
-    <row r="59" ht="22.5" hidden="1" customHeight="1">
+    <row r="59" ht="22.5" customHeight="1">
       <c r="A59" s="8">
         <v>46239.707476006944</v>
       </c>
@@ -3484,7 +3477,7 @@
       </c>
       <c r="AA59" s="11"/>
     </row>
-    <row r="60" ht="22.5" hidden="1" customHeight="1">
+    <row r="60" ht="22.5" customHeight="1">
       <c r="A60" s="8">
         <v>46239.79803805555</v>
       </c>
@@ -3541,7 +3534,7 @@
       </c>
       <c r="AA60" s="11"/>
     </row>
-    <row r="61" ht="22.5" hidden="1" customHeight="1">
+    <row r="61" ht="22.5" customHeight="1">
       <c r="A61" s="8">
         <v>46239.82072309028</v>
       </c>
@@ -3577,7 +3570,7 @@
       </c>
       <c r="AA61" s="11"/>
     </row>
-    <row r="62" ht="22.5" hidden="1" customHeight="1">
+    <row r="62" ht="22.5" customHeight="1">
       <c r="A62" s="8">
         <v>46241.55575290509</v>
       </c>
@@ -3639,7 +3632,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="63" ht="22.5" hidden="1" customHeight="1">
+    <row r="63" ht="22.5" customHeight="1">
       <c r="A63" s="8">
         <v>46241.71240017361</v>
       </c>
@@ -3713,7 +3706,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="64" ht="22.5" hidden="1" customHeight="1">
+    <row r="64" ht="22.5" customHeight="1">
       <c r="A64" s="8">
         <v>46242.65253738426</v>
       </c>
@@ -3742,7 +3735,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="65" ht="22.5" hidden="1" customHeight="1">
+    <row r="65" ht="22.5" customHeight="1">
       <c r="A65" s="8">
         <v>46243.3566297338</v>
       </c>
@@ -3789,7 +3782,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="66" ht="22.5" hidden="1" customHeight="1">
+    <row r="66" ht="22.5" customHeight="1">
       <c r="A66" s="8">
         <v>46243.69412138889</v>
       </c>
@@ -3824,7 +3817,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="67" ht="22.5" hidden="1" customHeight="1">
+    <row r="67" ht="22.5" customHeight="1">
       <c r="A67" s="8">
         <v>46244.65016612269</v>
       </c>
@@ -3889,7 +3882,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="68" ht="22.5" hidden="1" customHeight="1">
+    <row r="68" ht="22.5" customHeight="1">
       <c r="A68" s="8">
         <v>46244.6941922338</v>
       </c>
@@ -3909,7 +3902,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="69" ht="22.5" hidden="1" customHeight="1">
+    <row r="69" ht="22.5" customHeight="1">
       <c r="A69" s="8">
         <v>46244.702560300924</v>
       </c>
@@ -4070,7 +4063,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="73" ht="22.5" hidden="1" customHeight="1">
+    <row r="73" ht="22.5" customHeight="1">
       <c r="A73" s="8">
         <v>46251.77397138889</v>
       </c>
@@ -4218,7 +4211,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="75" ht="22.5" hidden="1" customHeight="1">
+    <row r="75" ht="22.5" customHeight="1">
       <c r="A75" s="8">
         <v>46252.27823043981</v>
       </c>
@@ -4247,7 +4240,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="76" ht="22.5" hidden="1" customHeight="1">
+    <row r="76" ht="22.5" customHeight="1">
       <c r="A76" s="8">
         <v>46257.441359282406</v>
       </c>
@@ -4282,7 +4275,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="77" ht="22.5" hidden="1" customHeight="1">
+    <row r="77" ht="22.5" customHeight="1">
       <c r="A77" s="8">
         <v>46258.5101271875</v>
       </c>
@@ -4619,7 +4612,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="85" ht="22.5" hidden="1" customHeight="1">
+    <row r="85" ht="22.5" customHeight="1">
       <c r="A85" s="8">
         <v>46273.591041747684</v>
       </c>
@@ -5000,7 +4993,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="94" ht="22.5" hidden="1" customHeight="1">
+    <row r="94" ht="22.5" customHeight="1">
       <c r="A94" s="8">
         <v>46275.42604790509</v>
       </c>
@@ -5194,7 +5187,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="98" ht="22.5" hidden="1" customHeight="1">
+    <row r="98" ht="22.5" customHeight="1">
       <c r="A98" s="8">
         <v>46277.80482196759</v>
       </c>
@@ -5308,6 +5301,77 @@
         <v>0.0</v>
       </c>
       <c r="Z100" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="101" ht="22.5" customHeight="1">
+      <c r="A101" s="8">
+        <v>46281.87963384259</v>
+      </c>
+      <c r="B101" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="C101" s="10">
+        <v>2026.0</v>
+      </c>
+      <c r="D101" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="G101" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="H101" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="I101" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="K101" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="L101" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="M101" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="N101" s="10">
+        <v>3.0</v>
+      </c>
+      <c r="O101" s="10">
+        <v>9.0</v>
+      </c>
+      <c r="P101" s="10">
+        <v>2.0</v>
+      </c>
+      <c r="Q101" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="R101" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="S101" s="10">
+        <v>10.0</v>
+      </c>
+      <c r="T101" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="U101" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="V101" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="W101" s="10">
+        <v>3.0</v>
+      </c>
+      <c r="X101" s="10">
+        <v>6.0</v>
+      </c>
+      <c r="Y101" s="10">
+        <v>6.0</v>
+      </c>
+      <c r="Z101" s="10" t="s">
         <v>31</v>
       </c>
     </row>
